--- a/apps/web/public/importmallar/importmall-produktionsgrupper.xlsx
+++ b/apps/web/public/importmallar/importmall-produktionsgrupper.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -98,6 +98,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -109,7 +110,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1" style="4"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
@@ -164,101 +165,108 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kolumner du inte behöver kan tas bort eller lämnas tomma, och kolumnernas ordning spelar ingen roll.</t>
+          <t xml:space="preserve">Ta bort kolumner du inte använder. Kolumnernas ordning spelar ingen roll.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">En tom cell lämnar normalt värdet orört på en befintlig post, utom i kolumner där tomt betyder något: Huvudleverantör och Staffel: från antal/Staffel: pris (Inköpspriser), Partiformningsregel (Artiklar) samt Kalkyl och Tidsenhet med Uppdatera befintliga operationer (Operationer). Vad tomt betyder står vid varje kolumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tal skrivs med decimalkomma eller punkt. Obligatoriska kolumner måste finnas med och vara ifyllda på varje rad.</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kolumn</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Obligatorisk</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Förklaring</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Exempel</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kod</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ja</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Produktionsgruppens kod, max 20 tecken (skiftlägesokänsligt). Finns koden redan uppdateras gruppen, annars skapas en ny; en kod som upprepas i filen hoppas över efter första raden.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PV</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Namn</t>
+          <t xml:space="preserve">Kod</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Produktionsgruppens namn, max 100 tecken. En ny grupp utan namn får koden som namn; tom cell lämnar ett befintligt namn orört.</t>
+          <t xml:space="preserve">Produktionsgruppens kod, max 20 tecken (skiftlägesokänsligt). Finns koden redan uppdateras gruppen, annars skapas en ny; en kod som upprepas i filen hoppas över efter första raden.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plåtverkstad</t>
+          <t xml:space="preserve">PV</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Namn</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Produktionsgruppens namn, max 100 tecken. En ny grupp utan namn får koden som namn; tom cell lämnar ett befintligt namn orört.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plåtverkstad</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Beskrivning</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fritext, max 2 000 tecken. Tom cell lämnar fältet orört.</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Laser, kantpress och svets</t>
         </is>
